--- a/forms/trg/Formulir_TRG_sca.xlsx
+++ b/forms/trg/Formulir_TRG_sca.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B31)</f>
+        <f>COUNTA(Anggota!B5:B32)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F31)</f>
+        <f>COUNTA(Anggota!F5:F32)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,19 +913,11 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Try Dharsana, M.Acc.</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Dr. Darwis Said, Ak., MSA., CSRA</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Environmental Accounting</t>
@@ -937,17 +929,17 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0009-0003-1947-8274</t>
+          <t>0000-0001-5843-6884</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6789754</t>
+          <t>6028021</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>59233713000</t>
+          <t>57222329927</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -962,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Rizky Utami, M.Acc. Fin</t>
+          <t>Muhammad Try Dharsana, M.Acc.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -977,16 +969,28 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Financial Accounting and Ocean Accounting</t>
+          <t>Environmental Accounting</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="12" t="n"/>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="12" t="n"/>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>0009-0003-1947-8274</t>
+        </is>
+      </c>
+      <c r="K6" s="11" t="inlineStr">
+        <is>
+          <t>6789754</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>59233713000</t>
+        </is>
+      </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -999,12 +1003,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Afdal, PhD., Ak.</t>
+          <t>Rizky Utami, M.Acc. Fin</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1014,28 +1018,16 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Environmental Management Accounting</t>
+          <t>Financial Accounting and Ocean Accounting</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-2623-8204</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="inlineStr">
-        <is>
-          <t>6057177</t>
-        </is>
-      </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>56884825100</t>
-        </is>
-      </c>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1048,12 +1040,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Hermita Arif, M.Com.</t>
+          <t>Afdal, PhD., Ak.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1063,7 +1055,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Islamic Social Finance, Personal Finance, Islamic Accounting</t>
+          <t>Environmental Management Accounting</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1072,17 +1064,17 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-5104-9355</t>
+          <t>0000-0003-2623-8204</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>6747858</t>
+          <t>6057177</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>57208670038</t>
+          <t>56884825100</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1097,12 +1089,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Nadhirah Nagu, SE., Ak., M.Si., CA., CSRA., CSRA., CSP., ACSAP</t>
+          <t>Hermita Arif, M.Com.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1112,7 +1104,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Sustainability Accounting and Sustainability Assurance</t>
+          <t>Islamic Social Finance, Personal Finance, Islamic Accounting</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1121,17 +1113,17 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-0759-1435</t>
+          <t>0000-0001-5104-9355</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>6025881</t>
+          <t>6747858</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>57204477667</t>
+          <t>57208670038</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1146,12 +1138,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Irdam Ferdiansah SE., M.ACC., Ph.D, Ak., CA.</t>
+          <t>Dr. Nadhirah Nagu, SE., Ak., M.Si., CA., CSRA., CSRA., CSP., ACSAP</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1161,7 +1153,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Management Accounting, Behavioural Accounting</t>
+          <t>Sustainability Accounting and Sustainability Assurance</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1170,17 +1162,17 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-7421-8297</t>
+          <t>0000-0002-0759-1435</t>
         </is>
       </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>6074513</t>
+          <t>6025881</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>54966872300</t>
+          <t>57204477667</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1195,22 +1187,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Professor Lu Aye</t>
+          <t>Muhammad Irdam Ferdiansah SE., M.ACC., Ph.D, Ak., CA.</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>The University of Melbourne</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Renewable Energy and Energy Efficiency</t>
+          <t>Management Accounting, Behavioural Accounting</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1219,11 +1211,19 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-5495-1683</t>
-        </is>
-      </c>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
+          <t>0000-0001-7421-8297</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>6074513</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>54966872300</t>
+        </is>
+      </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1236,22 +1236,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Nurul Fitrah Islamiah, S. Tr. Ak., M. Ak.</t>
+          <t>Professor Lu Aye</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Politeknik Negeri Ujung Pandang</t>
+          <t>The University of Melbourne</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Environmental Accounting</t>
+          <t>Renewable Energy and Energy Efficiency</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0009-0005-0911-8843</t>
+          <t>0000-0002-5495-1683</t>
         </is>
       </c>
       <c r="K12" s="12" t="n"/>
@@ -1277,29 +1277,33 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Alia Rezki Amalia, S. Ak., M. Ak</t>
+          <t>Nurul Fitrah Islamiah, S. Tr. Ak., M. Ak.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Universitas Negeri Makassar</t>
+          <t>Politeknik Negeri Ujung Pandang</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Environmental Management Accounting</t>
+          <t>Environmental Accounting</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>0009-0005-0911-8843</t>
+        </is>
+      </c>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="12" t="n"/>
       <c r="M13" s="11" t="inlineStr">
@@ -1314,12 +1318,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Ambarwati Akib, S. Ak., M. Ak.</t>
+          <t>Alia Rezki Amalia, S. Ak., M. Ak</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1329,7 +1333,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Environmental Accounting</t>
+          <t>Environmental Management Accounting</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1351,33 +1355,29 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Marannu Paledung, SE., M.Ak</t>
+          <t>Ambarwati Akib, S. Ak., M. Ak.</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Pattimura University</t>
+          <t>Universitas Negeri Makassar</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Environmental Accounting and Market Based Research Accounting</t>
+          <t>Environmental Accounting</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-8862-4325</t>
-        </is>
-      </c>
+      <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
       <c r="M15" s="11" t="inlineStr">
@@ -1392,22 +1392,22 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Asriani Junaid, SE., Ak., M.SA., CA., CSRS., CSRA</t>
+          <t>Marannu Paledung, SE., M.Ak</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Universitas Muslim Indonesia</t>
+          <t>Pattimura University</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Management Accounting, Behavioral Accounting</t>
+          <t>Environmental Accounting and Market Based Research Accounting</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1416,14 +1416,10 @@
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-3287-3220</t>
-        </is>
-      </c>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>6170078</t>
-        </is>
-      </c>
+          <t>0000-0001-8862-4325</t>
+        </is>
+      </c>
+      <c r="K16" s="12" t="n"/>
       <c r="L16" s="12" t="n"/>
       <c r="M16" s="11" t="inlineStr">
         <is>
@@ -1437,22 +1433,22 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Astri Dyatriarini</t>
+          <t>Asriani Junaid, SE., Ak., M.SA., CA., CSRS., CSRA</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Universitas Muslim Indonesia</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Environmental Accounting</t>
+          <t>Management Accounting, Behavioral Accounting</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -1461,10 +1457,14 @@
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-2124-1383</t>
-        </is>
-      </c>
-      <c r="K17" s="12" t="n"/>
+          <t>0000-0003-3287-3220</t>
+        </is>
+      </c>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>6170078</t>
+        </is>
+      </c>
       <c r="L17" s="12" t="n"/>
       <c r="M17" s="11" t="inlineStr">
         <is>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Poppy Ruddin</t>
+          <t>Astri Dyatriarini</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1493,14 +1493,18 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Critical Accounting</t>
+          <t>Environmental Accounting</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
       <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-2124-1383</t>
+        </is>
+      </c>
       <c r="K18" s="12" t="n"/>
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="11" t="inlineStr">
@@ -1515,38 +1519,30 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Agnes Eyne Banea, SE., MSA., CPFM., CTA., ACPA</t>
+          <t>Poppy Ruddin</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Sekolah Tinggi Bisnis dan Manajemen Dua Saudara Bitung</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Environmental (Waste) Accounting</t>
+          <t>Critical Accounting</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
       <c r="I19" s="12" t="n"/>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>0009-0006-3637-0638</t>
-        </is>
-      </c>
-      <c r="K19" s="11" t="inlineStr">
-        <is>
-          <t>6785122</t>
-        </is>
-      </c>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="11" t="inlineStr">
         <is>
@@ -1558,18 +1554,46 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="11" t="n"/>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Agnes Eyne Banea, SE., MSA., CPFM., CTA., ACPA</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Sekolah Tinggi Bisnis dan Manajemen Dua Saudara Bitung</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Environmental (Waste) Accounting</t>
+        </is>
+      </c>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
       <c r="I20" s="12" t="n"/>
-      <c r="J20" s="12" t="n"/>
-      <c r="K20" s="12" t="n"/>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>0009-0006-3637-0638</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>6785122</t>
+        </is>
+      </c>
       <c r="L20" s="12" t="n"/>
-      <c r="M20" s="12" t="n"/>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1758,15 +1782,32 @@
       <c r="L31" s="12" t="n"/>
       <c r="M31" s="12" t="n"/>
     </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/forms/trg/Formulir_TRG_sca.xlsx
+++ b/forms/trg/Formulir_TRG_sca.xlsx
@@ -916,7 +916,11 @@
           <t>Dr. Darwis Said, Ak., MSA., CSRA</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
